--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>計画の表現、方針、記載の有無について打合せで確認いただく事項。決定すれば本文の文言が確定する。</t>
+          <t>計画の表現、方針、記載の有無について打合せで確認いただく事項（25件）。決定すれば本文の文言が確定する。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>データ源、指標の定義、算定方法、基準時点について確認いただく事項。決定すれば数値が確定する。</t>
+          <t>データ源、指標の定義、算定方法、基準時点について確認いただく事項（31件）。決定すれば数値が確定する。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1179,30 +1179,64 @@
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>第10稿（4次）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>R8.7.30</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析の反映</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>見える化δ（介護サービス自給率）・D49（地域差指数）・C1（保険料と必要額）の受領により、地域差の分析（15シート）を作成し、本文の記述を改めた。①第7期の保険料基準額6,077円を原典で確認し［要確認］を外した。②地域差指数の3要素の分解による按分の記述を撤回した（受給率×受給者単価は給付月額指数に一致しない）。③給付水準の評価に管内の位置と長期の推移を加えた（管内8〜10位、17年間の伸びは管内16位）。④施設・居住系の給付のうち区域外の事業所によるものの割合を確定した（東川23.2％・美瑛24.7％・東神楽34.5％）。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析（15シート）、第9期評価のレッドチームレビュー No.27〜29</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節・第3節
+第3章第5節
+第6章第5節・第6節</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>第10稿（3次）</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>R8.7.29</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>体裁の整理</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>①表紙の【第9稿からの主な変更】の表（6行）を削除し、本表01シートへ移した。②目次の【新設】4箇所及びページ番号に関する注記を削除し、本表02シートへ移した。③本文の注記56箇所のうち42箇所を削除し、確認事項として本表03・04シートへ移した。本文に残したのは、図表を読むために必要な出典・単位・欠測・数値の性質及び記号の意味の14箇所である。④巻末の「本素案の取扱い」の段落を削除し、本表01シートへ移した。⑤削除した注記のうち計画の読み手に必要な内容は、注記ではなく本文の文中に移した（第1章第7節の訪問・通所困難地域の考え方、第1章第9節の特定地域の判定単位及び基準②のもう一方の要件）。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>発注者からの指示（令和8年7月29日）</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>表紙
 目次
@@ -1211,155 +1245,155 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映した第10稿である。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="8" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>【今後の稿の予定】</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>第11稿</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>計画骨子案</t>
+          <t>第11稿</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画素案（提出版）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="96" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="21" ht="96" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）稿の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）第10稿（2次）の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価のレッドチームレビュー」08シートに記載している。</t>
         </is>
@@ -1370,12 +1404,12 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1780,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2720,126 +2754,195 @@
     </row>
     <row r="26" ht="88" customHeight="1">
       <c r="A26" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>図表全体</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス自給率（δ）の計画本文への掲載</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>見える化δ（介護サービス自給率）を令和8年7月30日に受領した。同指標には「本指標は自治体向けのため取り扱いに注意」と明記されている。3町の6区分平均は美瑛77.5％・東川67.1％・東神楽63.2％である。</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>δを計画本文及び図表集に掲載してよいか。掲載できない場合、分析資料にとどめ本文には所見のみを記述する。</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>第6章第5節</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>給付費の地域内還流を整備の意義として位置づけるか</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>3町の自給率が63〜78％であることから、給付費の22〜37％相当が区域外の事業所に向かっている。区域内整備には、サービスへのアクセスの確保に加えて給付費の地域内還流という意義がある。</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>区域内整備の意義として給付費の地域内還流を位置づけるか。介護分野を地域の産業として扱うかは方針の選択である。</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>発注者・策定委員会</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>第3章第5節</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>給付水準の評価に管内の位置と長期の推移を加えるか</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>給付月額指数1.08は全国を8％上回るが、上川管内21保険者では8〜10位で管内中位値1.05に近い。平成21年度は管内1位であった給付月額が令和7年度は12位となり、17年間の伸び率＋25.1％は管内16位（管内平均＋46.4％）である。</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>第9期の評価を「水準は全国を上回るが管内では平均並みであり、17年間の伸びは管内で小さい」という両面の記述に改めてよいか。</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>発注者・策定委員会</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="88" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>第2章第1節</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>第9期計画との人口の基準の違いの説明</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>第9期計画の人口・高齢化率は住民基本台帳（各年10月1日現在）による。第10期の推計及び見える化のデータは国勢調査及び社人研推計によるため、同じ令和5年でも総人口で382人、高齢化率で1.1ポイントの差が生じる。</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>基準を国勢調査・社人研に統一する方針を本文に明記してよいか。第9期計画の数値と一致しないことを本文で説明する必要があるか。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>発注者・策定委員会</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B29" s="4">
-        <f>COUNTIF(G5:G26,"完了")</f>
-        <v/>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B30" s="4">
-        <f>COUNTIF(G5:G26,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B31" s="4">
-        <f>COUNTIF(G5:G26,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
       <c r="B32" s="4">
-        <f>COUNTIF(G5:G26,"未着手")</f>
+        <f>COUNTIF(G5:G29,"完了")</f>
         <v/>
       </c>
       <c r="C32" s="5" t="inlineStr"/>
@@ -2851,13 +2954,13 @@
       <c r="I32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(G5:G26,"対象外")</f>
+        <f>COUNTIF(G5:G29,"実施中")</f>
         <v/>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
@@ -2868,19 +2971,73 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
     </row>
-    <row r="35" ht="96" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>注1）本シートの22件は、いずれも「計画に何をどう書くか」の決定を求めるものである。数値そのものは確定しているか、又は本シートの決定とは独立に確定する。注2）決定の主体が策定委員会となるもの（No.4・9・11・13・21・22）は、第1回委員会の付議事項として整理する。注3）北海道との協議を要するもの（No.5・6・10・15・16）は、いずれも区域内に事業所・施設が存在しないことに起因する。北海道への照会を1回にまとめることを想定している。</t>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>COUNTIF(G5:G29,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>COUNTIF(G5:G29,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>COUNTIF(G5:G29,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="96" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>注1）本シートの25件は、いずれも「計画に何をどう書くか」の決定を求めるものである。数値そのものは確定しているか、又は本シートの決定とは独立に確定する。注2）決定の主体が策定委員会となるもの（No.4・9・11・13・21・22・24・25）は、第1回委員会の付議事項として整理する。注3）北海道との協議を要するもの（No.5・6・10・15・16）は、いずれも区域内に事業所・施設が存在しないことに起因する。北海道への照会を1回にまとめることを想定している。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G26">
+  <conditionalFormatting sqref="G5:G29">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2898,7 +3055,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2912,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3337,7 +3494,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>決算及び基金の積立・取崩実績により剰余額を確定したい。第7期の保険料基準額（6,077円か5,900円か）も条例で確認したい。</t>
+          <t>決算及び基金の積立・取崩実績により剰余額を確定したい。剰余の月額（第7期＋159円・第8期＋66円・第9期2年＋385円）は見える化C1により確定した（令和8年7月30日受領）。第7期の基準額6,077円も同系列で確認したため、条例による確認は不要となった。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3357,7 +3514,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>No.9・No.10</t>
+          <t>No.9</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -4238,135 +4395,216 @@
     </row>
     <row r="32" ht="96" customHeight="1">
       <c r="A32" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>地域差指数の分解を要因の按分に用いない方針</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>受給率×受給者単価は給付月額指数に一致しない。上川管内21保険者のうち16保険者で0.03を超えてずれ、全保険者で正の方向に偏る（平均＋0.063、大雪＋0.065）。給付月額指数と認定率指数は性・年齢調整後であるが、受給率指数と受給者単価指数には調整の表示がない。</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>分解による按分の記述を撤回し、4要素を並列の指標として示す方針でよいか。要因の特定は管内21保険者の分散を説明する方法（回帰）による。</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節・第3章の記述</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>No.16</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>自給率の6区分平均の算定方法</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>算定できる区分の単純平均としている（東川町・東神楽町は多機能系が算定できないため5区分）。給付額による加重平均とは一致しない。</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>単純平均とするか、給付額による加重平均とするか。加重平均には町別のサービス区分別給付費を要する。</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節の自給率の表</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>No.17</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="96" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>第9期の剰余の確定と基金への積立の確認</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>剰余の月額は見える化C1により確定した（第7期＋159円・第8期＋66円・第9期2年＋385円）。第7期の基準額6,077円も同系列で確認した。令和6・7年度は年度途中までの集計である。</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>剰余が基金に積み立てられた額と一致するかを決算・基金実績で確認したい。令和8年度末の基金残高見込と第10期の取崩方針。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節の保険料試算</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>No.9</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>資料6</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>見える化システムで取得できない系列</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>次の系列は当広域連合についてデータ登録がなく取得できないことを確認している（令和8年7月29日）。δ（介護サービス自給率）、H1・H2（介護人材の必要数）、J（認知症施策）、L（医療機関・看取り・診療報酬側の連携指標）。</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>これらの系列について、保険者側で登録が可能なものがあるか。代替手段（資料6に記載）でよいか。</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>資料6の対応表</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr"/>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B35" s="4">
-        <f>COUNTIF(G5:G32,"完了")</f>
-        <v/>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B36" s="4">
-        <f>COUNTIF(G5:G32,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B37" s="4">
-        <f>COUNTIF(G5:G32,"確認待ち")</f>
-        <v/>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="5" t="inlineStr"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
       <c r="B38" s="4">
-        <f>COUNTIF(G5:G32,"未着手")</f>
+        <f>COUNTIF(G5:G35,"完了")</f>
         <v/>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
@@ -4379,13 +4617,13 @@
       <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(G5:G32,"対象外")</f>
+        <f>COUNTIF(G5:G35,"実施中")</f>
         <v/>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
@@ -4397,89 +4635,146 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
     </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B40" s="4">
+        <f>COUNTIF(G5:G35,"確認待ち")</f>
+        <v/>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B41" s="4">
+        <f>COUNTIF(G5:G35,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B42" s="4">
+        <f>COUNTIF(G5:G35,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>資料の提供を要するか</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>資料の提供を要する</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B45" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27、No.29、No.30、No.31</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>提供済の資料・方針の決定で足りる</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>提供済の資料・方針の決定で足りる</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>No.2、No.4、No.6、No.10、No.12、No.13、No.14、No.18、No.19、No.20、No.22、No.23、No.25、No.28</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="8" t="n"/>
-    </row>
-    <row r="45" ht="96" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>注1）本シートの28件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち14件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="8" t="n"/>
+    </row>
+    <row r="48" ht="96" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>注1）本シートの31件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち17件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27・31）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="C46:J46"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G32">
+  <conditionalFormatting sqref="G5:G35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4497,7 +4792,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1179,30 +1179,63 @@
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>第10稿（5次）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>R8.7.30</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の着手</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>人口推計の基礎を社人研推計とすることが決定したことを受け、将来推計の第1段階（人口と認定者数）を行った。①第2章第1節に人口推計の基礎と第9期計画との差の理由を記載する。②第6章第1節の認定者数の見込みに3シナリオの算定結果を反映する。③第10期期間中は65歳以上人口がほぼ横ばいで、増えるのは80〜84歳と85歳以上のみであることを明記する。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>見える化A系列、将来推計（8シート）</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>第2章第1節
+第6章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>第10稿（4次）</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>R8.7.30</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>地域差の分析の反映</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>見える化δ（介護サービス自給率）・D49（地域差指数）・C1（保険料と必要額）の受領により、地域差の分析（15シート）を作成し、本文の記述を改めた。①第7期の保険料基準額6,077円を原典で確認し［要確認］を外した。②地域差指数の3要素の分解による按分の記述を撤回した（受給率×受給者単価は給付月額指数に一致しない）。③給付水準の評価に管内の位置と長期の推移を加えた（管内8〜10位、17年間の伸びは管内16位）。④施設・居住系の給付のうち区域外の事業所によるものの割合を確定した（東川23.2％・美瑛24.7％・東神楽34.5％）。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>地域差の分析（15シート）、第9期評価のレッドチームレビュー No.27〜29</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>第2章第2節・第3節
 第3章第5節
@@ -1210,33 +1243,33 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="140" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>第10稿（3次）</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>R8.7.29</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>体裁の整理</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>①表紙の【第9稿からの主な変更】の表（6行）を削除し、本表01シートへ移した。②目次の【新設】4箇所及びページ番号に関する注記を削除し、本表02シートへ移した。③本文の注記56箇所のうち42箇所を削除し、確認事項として本表03・04シートへ移した。本文に残したのは、図表を読むために必要な出典・単位・欠測・数値の性質及び記号の意味の14箇所である。④巻末の「本素案の取扱い」の段落を削除し、本表01シートへ移した。⑤削除した注記のうち計画の読み手に必要な内容は、注記ではなく本文の文中に移した（第1章第7節の訪問・通所困難地域の考え方、第1章第9節の特定地域の判定単位及び基準②のもう一方の要件）。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>発注者からの指示（令和8年7月29日）</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>表紙
 目次
@@ -1245,155 +1278,155 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映した第10稿である。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="8" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>【今後の稿の予定】</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>第11稿</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>計画骨子案</t>
+          <t>第11稿</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画素案（提出版）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="96" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="22" ht="96" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）稿の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）第10稿（2次）の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価のレッドチームレビュー」08シートに記載している。</t>
         </is>
@@ -1401,15 +1434,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C16:E16"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3346,7 +3379,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>東川町の将来推計の基礎</t>
+          <t>東川町の将来推計の基礎【決定済（R8.7.30）】</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -3356,7 +3389,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>社人研推計（システムの初期値）をそのまま用いるか、3町の総合計画等による推計人口へ差し替えるか。差し替える場合、令和6年・令和7年の住基実績により検証したい。</t>
+          <t>社人研推計（システムの初期値）をそのまま用いることが決定した（令和8年7月30日。広域連合からの意向がない場合は見える化の値による）。令和6年・令和7年の住基実績を受領した際は乖離を確認し、大きい場合は第2章に注記する（推計の基礎そのものは変更しない）。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3366,7 +3399,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -3379,7 +3412,11 @@
           <t>No.3</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>社人研推計を採用</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -4082,22 +4119,22 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>認定率の設定方法</t>
+          <t>階級別認定率のシナリオの選択</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の需要推計は実績を上回っており、令和6年度は▲2.9％、令和7年度は▲3.5％の乖離が生じている。第10期では認定率を年齢階級別に設定し、軽度と中重度で方向が異なることを反映する案としている。</t>
+          <t>認定率を年齢階級別（65〜74歳・75〜84歳・85歳以上）に設定した。①現状固定／②トレンド継続〈受託者の推奨〉／③令和元年水準へ回帰の3シナリオを算定した（将来推計03・04シート）。令和11年度の認定者数は①2,044人・②2,004人・③2,112人である。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>認定率を年齢階級別に設定する方針でよいか。重度化の速度をどう置くか（全国並みに収束／現状継続／改善継続）。</t>
+          <t>いずれのシナリオを計画に採用するか。②を基本とし③を保険料の安全側の確認として併用する案でよいか。年次評価で階級別認定率の実績を確認し、乖離が2年続けて2％を超えた場合に中間年で見直す仕組みでよいか。</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>第6章第1節の認定者数見込み</t>
+          <t>第6章第1節の認定者数見込み、第2節以降の全体</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1179,63 +1179,99 @@
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>第10稿（6次）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>R8.7.30</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>本文への反映</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>受領した見える化の各系列（δ 自給率、D49 地域差指数、C1 保険料、A 人口）による分析結果を本文に反映した。①第2章第2節1を「給付水準の高さの要因」から「給付水準の位置」に改め、地域差指数の4要素を並列で示し、掛け合わせても給付月額の指数に一致しないことを明記した。あわせて上川管内における位置（8〜10位）と17年間の推移（管内1位から12位、伸び率は管内16位）を追加した。②第2章第3節に「区域内の事業所による給付の割合（介護サービス自給率）」を新設し、3町の6区分別の自給率と区域外の事業所による給付の割合を掲載した。③第3章第5節に「長期でみた到達点」を新設し、給付水準・認定率・財政の長期の推移を整理した。第10期の重点を重度化防止から介護予防へ移す根拠を明記した。④第6章第6節に保険料と必要保険料月額との関係（管内21保険者中6のみ剰余）を追加した。⑤第1章第6節に推計の見直しの手順を新設し、階級別認定率の実績を年次評価で確認する仕組みを位置づけた。⑥第2章第8節の中長期推計の表を新推計に差し替え、総給付費は第3段階での算定を待つため［要確認］とした。⑦資料6の別表「五」を「一部対応」から「対応済」に改めた。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>地域差の分析（15シート）、人口推計の基礎の検証（9シート）、将来推計（8シート）、第9期評価のレッドチームレビュー</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>第1章第6節
+第2章第2節・第3節・第8節
+第3章第5節
+第6章第6節
+資料6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>第10稿（5次）</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>R8.7.30</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>将来推計の着手</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>人口推計の基礎を社人研推計とすることが決定したことを受け、将来推計の第1段階（人口と認定者数）を行った。①第2章第1節に人口推計の基礎と第9期計画との差の理由を記載する。②第6章第1節の認定者数の見込みに3シナリオの算定結果を反映する。③第10期期間中は65歳以上人口がほぼ横ばいで、増えるのは80〜84歳と85歳以上のみであることを明記する。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>見える化A系列、将来推計（8シート）</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>第2章第1節
 第6章第1節</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="140" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>第10稿（4次）</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>R8.7.30</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>地域差の分析の反映</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>見える化δ（介護サービス自給率）・D49（地域差指数）・C1（保険料と必要額）の受領により、地域差の分析（15シート）を作成し、本文の記述を改めた。①第7期の保険料基準額6,077円を原典で確認し［要確認］を外した。②地域差指数の3要素の分解による按分の記述を撤回した（受給率×受給者単価は給付月額指数に一致しない）。③給付水準の評価に管内の位置と長期の推移を加えた（管内8〜10位、17年間の伸びは管内16位）。④施設・居住系の給付のうち区域外の事業所によるものの割合を確定した（東川23.2％・美瑛24.7％・東神楽34.5％）。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>地域差の分析（15シート）、第9期評価のレッドチームレビュー No.27〜29</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>第2章第2節・第3節
 第3章第5節
@@ -1243,33 +1279,33 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="140" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>第10稿（3次）</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>R8.7.29</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>体裁の整理</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>①表紙の【第9稿からの主な変更】の表（6行）を削除し、本表01シートへ移した。②目次の【新設】4箇所及びページ番号に関する注記を削除し、本表02シートへ移した。③本文の注記56箇所のうち42箇所を削除し、確認事項として本表03・04シートへ移した。本文に残したのは、図表を読むために必要な出典・単位・欠測・数値の性質及び記号の意味の14箇所である。④巻末の「本素案の取扱い」の段落を削除し、本表01シートへ移した。⑤削除した注記のうち計画の読み手に必要な内容は、注記ではなく本文の文中に移した（第1章第7節の訪問・通所困難地域の考え方、第1章第9節の特定地域の判定単位及び基準②のもう一方の要件）。</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>発注者からの指示（令和8年7月29日）</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>表紙
 目次
@@ -1278,155 +1314,155 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映した第10稿である。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="8" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>【今後の稿の予定】</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>第11稿</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>計画骨子案</t>
+          <t>第11稿</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画素案（提出版）</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="96" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）稿の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）第10稿（2次）の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価のレッドチームレビュー」08シートに記載している。</t>
         </is>
@@ -1435,14 +1471,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>人口推計の基礎を社人研推計とすることが決定したことを受け、将来推計の第1段階（人口と認定者数）を行った。①第2章第1節に人口推計の基礎と第9期計画との差の理由を記載する。②第6章第1節の認定者数の見込みに3シナリオの算定結果を反映する。③第10期期間中は65歳以上人口がほぼ横ばいで、増えるのは80〜84歳と85歳以上のみであることを明記する。</t>
+          <t>人口推計の基礎について社人研推計を受託者の案とし、これを作業上の前提として仮に置いたうえで、将来推計の第1段階（人口と認定者数）を試算した。①第2章第1節に人口推計の基礎と第9期計画との差の理由を記載する。②第6章第1節の認定者数の見込みに3シナリオの算定結果を反映する。③第10期期間中は65歳以上人口がほぼ横ばいで、増えるのは80〜84歳と85歳以上のみであることを明記する。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>東川町の将来推計の基礎【決定済（R8.7.30）】</t>
+          <t>東川町の将来推計の基礎【受託者の案・意向確認待ち】</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>社人研推計（システムの初期値）をそのまま用いることが決定した（令和8年7月30日。広域連合からの意向がない場合は見える化の値による）。令和6年・令和7年の住基実績を受領した際は乖離を確認し、大きい場合は第2章に注記する（推計の基礎そのものは変更しない）。</t>
+          <t>受託者は、社人研推計（システムの初期値）をそのまま用いることを案とし、これを作業上の前提として仮に置いたうえで第1段階を試算している。キックオフ会議でご意向を確認したうえで基礎を採用する（別冊のヒアリングシート 項目6-1）。他の系列によるとのご意向がある場合は第1段階を再計算する。令和6年・令和7年の住基実績を受領した際は乖離を確認し、大きい場合は第2章に注記する。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -3448,11 +3448,7 @@
           <t>No.3</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>社人研推計を採用</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="96" customHeight="1">
       <c r="A10" s="4" t="n">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -684,18 +684,18 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>稿別の変更内容を管理する。第9期計画の体裁では表紙に変更履歴を置いていないため、本文からは削除した。</t>
+          <t>版別の変更内容を管理する。第9期計画の体裁では表紙に変更履歴を置いていないため、本文からは削除した。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>表紙の【第9稿からの主な変更】の表（6行）
+          <t>表紙の【前版からの主な変更】の表（6行）
 巻末の「本素案の取扱い」の段落</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>受託者が稿の更新ごとに追記</t>
+          <t>受託者が版の更新ごとに追記</t>
         </is>
       </c>
     </row>
@@ -712,18 +712,18 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>前稿からの新設・変更箇所を節単位で管理する。目次は計画の構成を示すものであり、作業の履歴を示す注記は目次に置かない。</t>
+          <t>前版からの新設・変更箇所を節単位で管理する。目次は計画の構成を示すものであり、作業の履歴を示す注記は目次に置かない。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>目次の【新設】4箇所
-「※ページ番号は最終組版時に更新します。【新設】は第9稿からの追加です。」</t>
+「※ページ番号は最終組版時に更新します。【新設】は前版からの追加です。」</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>受託者が稿の更新ごとに追記</t>
+          <t>受託者が版の更新ごとに追記</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>第9期評価のレッドチームレビュー</t>
+          <t>第9期評価の自己点検記録</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>注1）本表への移動により、計画素案（第10稿）の本文からは注記42箇所を削除し、14箇所を残した（残した基準は05シート）。表紙の変更履歴の表及び巻末の取扱いの段落も削除した。注2）確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残す方針を継続する。本表A・Bの確認事項が解消された時点で、該当箇所を確定値に置き換える。注3）打合せでは、A（文言）とB（数値・計算根拠）を分けて進めることを想定している。Aは策定委員会での議論に直結し、Bは資料の提供と算定の作業に直結するため、決定の主体と所要時間が異なる。</t>
+          <t>注1）本表への移動により、計画素案の本文からは注記42箇所を削除し、14箇所を残した（残した基準は05シート）。表紙の変更履歴の表及び巻末の取扱いの段落も削除した。注2）確定していない数値は、本文では［要協議］［要確認］［要内訳］として空欄扱いのまま残す方針を継続する。本表A・Bの確認事項が解消された時点で、該当箇所を確定値に置き換える。注3）打合せでは、A（文言）とB（数値・計算根拠）を分けて進めることを想定している。Aは策定委員会での議論に直結し、Bは資料の提供と算定の作業に直結するため、決定の主体と所要時間が異なる。</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
     <row r="5" ht="140" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>第9稿</t>
+          <t>令和8年7月　初版</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="6" ht="140" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月　第2版</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="7" ht="140" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>第10稿（2次）</t>
+          <t>令和8年7月29日　是正版</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>受託者の自己点検（レッドチームレビュー）及び主張の棚卸しにより、推論・仮説を断定形で記述していた10箇所を是正した。①「〜に由来する」を要因の特定を意味しない表現に改めた（給付水準の要因、訪問介護の利用強度）。②地域密着型通所介護の給付減について「稼働率の低下による」を「稼働率の低下が疑われる」に改めた。③朗根内地区の訪問・通所困難地域の判定について、判定の根拠となる事業所の実施地域を確認していないことを明記した。④施設入所志向について「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改めた。</t>
+          <t>受託者の自己点検（自己点検記録）及び主張の棚卸しにより、推論・仮説を断定形で記述していた10箇所を是正した。①「〜に由来する」を要因の特定を意味しない表現に改めた（給付水準の要因、訪問介護の利用強度）。②地域密着型通所介護の給付減について「稼働率の低下による」を「稼働率の低下が疑われる」に改めた。③朗根内地区の訪問・通所困難地域の判定について、判定の根拠となる事業所の実施地域を確認していないことを明記した。④施設入所志向について「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改めた。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>第9期評価のレッドチームレビュー（指摘26件）、主張の根拠水準の棚卸しと再レビュー（主張46件・断定8件）</t>
+          <t>第9期評価の自己点検記録（指摘26件）、主張の根拠水準の棚卸しと再レビュー（主張46件・断定8件）</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>第10稿（6次）</t>
+          <t>令和8年7月30日　本文反映版</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>地域差の分析（15シート）、人口推計の基礎の検証（9シート）、将来推計（8シート）、第9期評価のレッドチームレビュー</t>
+          <t>地域差の分析（15シート）、人口推計の基礎の検証（9シート）、将来推計（8シート）、第9期評価の自己点検記録</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="9" ht="140" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>第10稿（5次）</t>
+          <t>令和8年7月30日　将来推計反映版</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1248,7 +1248,7 @@
     <row r="10" ht="140" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>第10稿（4次）</t>
+          <t>令和8年7月30日　地域差反映版</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>地域差の分析（15シート）、第9期評価のレッドチームレビュー No.27〜29</t>
+          <t>地域差の分析（15シート）、第9期評価の自己点検記録 No.27〜29</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="11" ht="140" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>第10稿（3次）</t>
+          <t>令和8年7月29日　体裁整理版</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>①表紙の【第9稿からの主な変更】の表（6行）を削除し、本表01シートへ移した。②目次の【新設】4箇所及びページ番号に関する注記を削除し、本表02シートへ移した。③本文の注記56箇所のうち42箇所を削除し、確認事項として本表03・04シートへ移した。本文に残したのは、図表を読むために必要な出典・単位・欠測・数値の性質及び記号の意味の14箇所である。④巻末の「本素案の取扱い」の段落を削除し、本表01シートへ移した。⑤削除した注記のうち計画の読み手に必要な内容は、注記ではなく本文の文中に移した（第1章第7節の訪問・通所困難地域の考え方、第1章第9節の特定地域の判定単位及び基準②のもう一方の要件）。</t>
+          <t>①表紙の【前版からの主な変更】の表（6行）を削除し、本表01シートへ移した。②目次の【新設】4箇所及びページ番号に関する注記を削除し、本表02シートへ移した。③本文の注記56箇所のうち42箇所を削除し、確認事項として本表03・04シートへ移した。本文に残したのは、図表を読むために必要な出典・単位・欠測・数値の性質及び記号の意味の14箇所である。④巻末の「本素案の取扱い」の段落を削除し、本表01シートへ移した。⑤削除した注記のうち計画の読み手に必要な内容は、注記ではなく本文の文中に移した（第1章第7節の訪問・通所困難地域の考え方、第1章第9節の特定地域の判定単位及び基準②のもう一方の要件）。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映した第10稿である。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
+          <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映したものである。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -1336,7 +1336,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>【今後の稿の予定】</t>
+          <t>【今後の版の予定】</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>第11稿</t>
+          <t>協議用素案（令和8年9月時点）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）稿の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）第10稿（2次）の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価のレッドチームレビュー」08シートに記載している。</t>
+          <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価の自己点検記録」08シートに記載している。</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>第10稿</t>
+          <t>令和8年7月</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>【新設】は第9稿からの追加です。</t>
+          <t>【新設】は前版からの追加です。</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>第10稿（2次）</t>
+          <t>是正版</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>第10稿（3次）</t>
+          <t>体裁整理版</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -951,7 +951,7 @@
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>主張の根拠水準の棚卸しと再レビュー</t>
+          <t>受託者の自己点検</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>第9期評価の自己点検記録</t>
+          <t>受託者の自己点検</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>受託者の自己点検（自己点検記録）及び主張の棚卸しにより、推論・仮説を断定形で記述していた10箇所を是正した。①「〜に由来する」を要因の特定を意味しない表現に改めた（給付水準の要因、訪問介護の利用強度）。②地域密着型通所介護の給付減について「稼働率の低下による」を「稼働率の低下が疑われる」に改めた。③朗根内地区の訪問・通所困難地域の判定について、判定の根拠となる事業所の実施地域を確認していないことを明記した。④施設入所志向について「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改めた。</t>
+          <t>受託者の自己点検（自己点検記録）及び主張の根拠水準の点検により、推論・仮説を断定形で記述していた10箇所を是正した。①「〜に由来する」を要因の特定を意味しない表現に改めた（給付水準の要因、訪問介護の利用強度）。②地域密着型通所介護の給付減について「稼働率の低下による」を「稼働率の低下が疑われる」に改めた。③朗根内地区の訪問・通所困難地域の判定について、判定の根拠となる事業所の実施地域を確認していないことを明記した。④施設入所志向について「支え手の有無で決まる」を「支え手の有無と強く結びついている」に改めた。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>第9期評価の自己点検記録（指摘26件）、主張の根拠水準の棚卸しと再レビュー（主張46件・断定8件）</t>
+          <t>受託者の自己点検（指摘26件）、受託者の自己点検（主張46件・断定8件）</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>受領した見える化の各系列（δ 自給率、D49 地域差指数、C1 保険料、A 人口）による分析結果を本文に反映した。①第2章第2節1を「給付水準の高さの要因」から「給付水準の位置」に改め、地域差指数の4要素を並列で示し、掛け合わせても給付月額の指数に一致しないことを明記した。あわせて上川管内における位置（8〜10位）と17年間の推移（管内1位から12位、伸び率は管内16位）を追加した。②第2章第3節に「区域内の事業所による給付の割合（介護サービス自給率）」を新設し、3町の6区分別の自給率と区域外の事業所による給付の割合を掲載した。③第3章第5節に「長期でみた到達点」を新設し、給付水準・認定率・財政の長期の推移を整理した。第10期の重点を重度化防止から介護予防へ移す根拠を明記した。④第6章第6節に保険料と必要保険料月額との関係（管内21保険者中6のみ剰余）を追加した。⑤第1章第6節に推計の見直しの手順を新設し、階級別認定率の実績を年次評価で確認する仕組みを位置づけた。⑥第2章第8節の中長期推計の表を新推計に差し替え、総給付費は第3段階での算定を待つため［要確認］とした。⑦資料6の別表「五」を「一部対応」から「対応済」に改めた。</t>
+          <t>受領した見える化の各系列（δ 自給率、D49 地域差指数、C1 保険料、A 人口）による分析結果を本文に反映した。①第2章第2節1を「給付水準の高さの要因」から「給付水準の位置」に改め、地域差指数の4要素を並列で示し、掛け合わせても給付月額の指数に一致しないことを明記した。あわせて上川管内における位置（8〜10位）と17年間の推移（管内1位から12位、伸び率は管内16位）を追加した。②第2章第3節に「区域内の事業所による給付の割合（介護サービス自給率）」を新設し、3町の区分別の自給率と区域外の事業所による給付の割合を掲載した。③第3章第5節に「長期でみた到達点」を新設し、給付水準・認定率・財政の長期の推移を整理した。第10期の重点を重度化防止から介護予防へ移す根拠を明記した。④第6章第6節に保険料と必要保険料月額との関係（管内21保険者中6のみ剰余）を追加した。⑤第1章第6節に推計の見直しの手順を新設し、階級別認定率の実績を年次評価で確認する仕組みを位置づけた。⑥第2章第8節の中長期推計の表を新推計に差し替え、総給付費は第3段階での算定を待つため［要確認］とした。⑦資料6の別表「五」を「一部対応」から「対応済」に改めた。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>地域差の分析（15シート）、人口推計の基礎の検証（9シート）、将来推計（8シート）、第9期評価の自己点検記録</t>
+          <t>地域差の分析（15シート）、人口推計の基礎の検証（9シート）、将来推計（8シート）、受託者の自己点検</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>地域差の分析（15シート）、第9期評価の自己点検記録 No.27〜29</t>
+          <t>地域差の分析（15シート）、受託者の自己点検 No.27〜29</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23" ht="96" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、「主張の根拠水準の棚卸しと再レビュー」03シート及び「第9期評価の自己点検記録」08シートに記載している。</t>
+          <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、受託者の自己点検及び受託者の自己点検に記載している。</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>経済的理由による未利用の記述</t>
+          <t>未利用の理由の把握の記述</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>見える化δ（介護サービス自給率）を令和8年7月30日に受領した。同指標には「本指標は自治体向けのため取り扱いに注意」と明記されている。3町の6区分平均は美瑛77.5％・東川67.1％・東神楽63.2％である。</t>
+          <t>見える化δ（介護サービス自給率）を令和8年7月30日に受領した。同指標には「本指標は自治体向けのため取り扱いに注意」と明記されている。3町の算定可能区分の単純平均（美瑛6区分、東川・東神楽5区分）は美瑛77.5％・東川67.1％・東神楽63.2％である。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>自給率の6区分平均の算定方法</t>
+          <t>自給率の平均の算定方法（算定可能区分が町により異なる）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>業務工程の進行を止めている確認事項（38件）</t>
+          <t>業務工程の進行を止めている確認事項（42件）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1314,155 +1314,190 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>令和8年8月31日　受領資料反映版</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>R8.8.31</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>受領資料の本文反映</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>見える化総括表の受領点検（7シート）、総合事業実施状況調査の受領点検（5シート）、年報月報の受領点検、令和6年度決算書の受領点検、基金条例の確認</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>第2章第1節
+第3章第1〜3節
+第4章第3節
+第6章第3節・第6節</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映したものである。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="8" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>【今後の版の予定】</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>協議用素案（令和8年9月時点）</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>計画骨子案</t>
+          <t>協議用素案（令和8年9月時点）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画素案（提出版）</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="96" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="24" ht="96" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、受託者の自己点検及び受託者の自己点検に記載している。</t>
         </is>
@@ -1470,15 +1505,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4432,12 +4467,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>第10期平均6,238円は、基金取崩0円、予定収納率99.0％、現行入力条件による自然体試算である。条例で採用する基準額ではなく、報酬改定、調整交付金、所得段階別補正、保険料抑制方針等の確定後に再計算する。必要保険料月額は保険給付費及び地域支援事業費から逆算した概算値である。</t>
+          <t>第10期平均6,238円は、基金取崩0円、予定収納率99.0％、現行入力条件による自然体試算である。条例で採用する基準額ではなく、報酬改定、調整交付金、所得段階別補正、保険料抑制方針等の確定後に再計算する。必要保険料月額は保険給付費及び地域支援事業費から逆算した概算値である。令和8年8月28日受領の年報により、現年度分の収納率の実績が令和6年度99.885％・令和7年度99.866％と確定した。見える化システムによる第9期の保険料基準額の実績は6,069円（準備基金取崩後・対計画比94％）である。</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>予定収納率99.0％の妥当性を第7〜9期の収納率実績により検証したい。基金の取崩方針と所得段階の設計（16段階を維持するか）。</t>
+          <t>予定収納率を実績（99.8％台）に即した水準に改めてよいか。収納率を0.8ポイント引き上げると基準額はおよそ0.8％低くなる。基金の取崩方針と所得段階の設計（16段階を維持するか）。</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1332,12 +1332,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。</t>
+          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。⑧第6章第3節3に標準給付費見込額（A）・地域支援事業費（B）・合計（①）を追加し、第6章第6節2に受託者による暫定算定（基本ケース月額6,684円）と前提を動かした場合の幅を加えた。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検（7シート）、総合事業実施状況調査の受領点検（5シート）、年報月報の受領点検、令和6年度決算書の受領点検、基金条例の確認</t>
+          <t>見える化総括表の受領点検（7シート）、総合事業実施状況調査の受領点検（5シート）、年報月報の受領点検、令和6年度決算書の受領点検、基金条例の確認、将来推計 第3段階（給付費と保険料）</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。⑧第6章第3節3に標準給付費見込額（A）・地域支援事業費（B）・合計（①）を追加し、第6章第6節2に受託者による暫定算定（基本ケース月額6,684円）と前提を動かした場合の幅を加えた。</t>
+          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。⑧第6章第3節3に標準給付費見込額（A）・地域支援事業費（B）・合計（①）を追加し、第6章第6節2に受託者による暫定算定（基本ケース月額6,755円）と前提を動かした場合の幅を加えた。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。⑧第6章第3節3に標準給付費見込額（A）・地域支援事業費（B）・合計（①）を追加し、第6章第6節2に受託者による暫定算定（基本ケース月額6,755円）と前提を動かした場合の幅を加えた。</t>
+          <t>令和8年8月28日及び31日に受領した資料を本文に反映した。①第2章第1節4の介護保険特別会計の推移に令和6年度の決算額と介護給付費準備基金の残高を加えた。②第3章第1節2の通いの場の統計に総合事業ベースの令和6年度実績（25箇所・330人・参加率3.53％）を加え、「平成29年度をピークに低下している」という記述を「令和2年度を底に回復したが国の水準8％を大きく下回る」に改めた。③第3章第2節に地域支援事業費の決算（183,384,259円）、通いの場の町別の展開状況、一般介護予防事業の実施状況を加えた。④第3章第3節に第9期の対計画比（主要8指標）と計画との乖離が大きい9サービスの表を新設した。⑤第4章第3節の代表KPI H15の基準値を確定した（令和6年度▲3.66％・令和7年度▲2.17％）。⑥第6章第3節2の地域支援事業費に令和6年度の決算の内訳を入れ、［要内訳］4件のうち3件を外した。⑦第6章第6節に見える化システムによる期別の保険料基準額、介護給付費準備基金の状況、保険料収納率と所得段階別被保険者数の実績を加えた。⑧第6章第3節3に標準給付費見込額（A）・地域支援事業費（B）・合計（①）を追加し、第6章第6節2に受託者による暫定算定（基本ケース月額6,740円）と前提を動かした場合の幅を加えた。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -3173,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4637,116 +4637,172 @@
     </row>
     <row r="35" ht="96" customHeight="1">
       <c r="A35" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>見込量の表の数値の出所</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節2（1）〜（3）の見込量の表の数値は、見える化システムの総括表・計画作成支援ツール・将来推計 第2段階のいずれとも一致せず、当方で出所を特定できていない。また表頭を「R8実績」としているが、令和8年度は約4か月分の実績しかなく、実績として掲げられる年度ではない。</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>見込量の表の数値を「サービス見込量の算定」の結果に差し替えてよいか。差し替えると見込量・給付費・保険料が一本の経路でつながる。表頭の「R8実績」は「R7実績」に改める。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節2の見込量の表</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>No.100</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="96" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>第6章第3節
+第6章第6節</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>給付費の算定に用いる基準年度と出所</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>現行の将来推計 第3段階は見える化システムの自然体推計に案C（総合戦略ベース）の置換率を乗じている。自然体推計には利用率及び単価の趨勢が織り込まれており、当方でその中身を分解できない。見える化システムの総括表による令和7年度実績を基準年度とし、認定者数の伸びのみを反映する置き方に改めると、算定上の月額基準額は6,740円から6,428円へ312円下がる。</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>採用パターンをどちらに置くか。サービス見込量 第1次概算（9月26日）より前に決定を要する。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階
+計画素案 第6章第3節・第6節</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>No.101</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>資料6</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>見える化システムで取得できない系列</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>次の系列は当広域連合についてデータ登録がなく取得できないことを確認している（令和8年7月29日）。δ（介護サービス自給率）、H1・H2（介護人材の必要数）、J（認知症施策）、L（医療機関・看取り・診療報酬側の連携指標）。</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>これらの系列について、保険者側で登録が可能なものがあるか。代替手段（資料6に記載）でよいか。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>資料6の対応表</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B38" s="4">
-        <f>COUNTIF(G5:G35,"完了")</f>
-        <v/>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B39" s="4">
-        <f>COUNTIF(G5:G35,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B40" s="4">
-        <f>COUNTIF(G5:G35,"確認待ち")</f>
+        <f>COUNTIF(G5:G37,"完了")</f>
         <v/>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
@@ -4759,13 +4815,13 @@
       <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(G5:G35,"未着手")</f>
+        <f>COUNTIF(G5:G37,"実施中")</f>
         <v/>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
@@ -4778,13 +4834,13 @@
       <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(G5:G35,"対象外")</f>
+        <f>COUNTIF(G5:G37,"確認待ち")</f>
         <v/>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
@@ -4796,89 +4852,127 @@
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
     </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B43" s="4">
+        <f>COUNTIF(G5:G37,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B44" s="4">
+        <f>COUNTIF(G5:G37,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>資料の提供を要するか</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>資料の提供を要する</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27、No.29、No.30、No.31</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="8" t="n"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27、No.29、No.30、No.31、No.32、No.33</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="8" t="n"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>提供済の資料・方針の決定で足りる</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B48" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>No.2、No.4、No.6、No.10、No.12、No.13、No.14、No.18、No.19、No.20、No.22、No.23、No.25、No.28</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="8" t="n"/>
-    </row>
-    <row r="48" ht="96" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>注1）本シートの31件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち17件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27・31）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="8" t="n"/>
+    </row>
+    <row r="50" ht="96" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>注1）本シートの33件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち19件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27・31）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C45:J45"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="C48:J48"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="C47:J47"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G35">
+  <conditionalFormatting sqref="G5:G37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4896,7 +4990,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -3173,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>No.100</t>
+          <t>―</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -4724,123 +4724,180 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>No.101</t>
+          <t>―</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="96" customHeight="1">
       <c r="A37" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>第2章第8節
+第6章第2節
+第6章第3節</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>中長期推計を見込量・給付費・保険料まで及ぼすか</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービス見通しを計画に定めることが必須となる。国の第10期基本指針（案）も2040年度を含む中長期推計を求めている。当方は認定者数について令和17年度2,228人・令和22年度2,288人を算定済みであるが、見込量・給付費・保険料は令和9〜11年度にとどまる。採用パターンの1人あたり給付費を固定し認定者数を乗じれば算定できる。</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度までの見込量・給付費・保険料を算定してよいか。算定の範囲（サービス種類別か区分計か、令和17年度も示すか）を決定する。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第8節・第6章第2節
+将来推計 第3段階</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="96" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>第6章第3節</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込み</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条第2項第2号は「各年度における地域支援事業の量の見込み」を基本的記載事項としているが、当方は費用の額のみを令和6年度決算の水準で置いており、量を算定していない。総合事業の令和7年度実績があれば、サービス区分ごとの利用者数を要支援認定者数の伸びで延長して算定できる。</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込みを算定してよいか。総合事業の令和7年度実績をご提供いただけるか。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第3節</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>No.19</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="96" customHeight="1">
+      <c r="A39" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>資料6</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>見える化システムで取得できない系列</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>次の系列は当広域連合についてデータ登録がなく取得できないことを確認している（令和8年7月29日）。δ（介護サービス自給率）、H1・H2（介護人材の必要数）、J（認知症施策）、L（医療機関・看取り・診療報酬側の連携指標）。</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>これらの系列について、保険者側で登録が可能なものがあるか。代替手段（資料6に記載）でよいか。</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>資料6の対応表</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="B40" s="4">
-        <f>COUNTIF(G5:G37,"完了")</f>
-        <v/>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="B41" s="4">
-        <f>COUNTIF(G5:G37,"実施中")</f>
-        <v/>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
       <c r="B42" s="4">
-        <f>COUNTIF(G5:G37,"確認待ち")</f>
+        <f>COUNTIF(G5:G39,"完了")</f>
         <v/>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
@@ -4853,13 +4910,13 @@
       <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>実施中</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(G5:G37,"未着手")</f>
+        <f>COUNTIF(G5:G39,"実施中")</f>
         <v/>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
@@ -4872,13 +4929,13 @@
       <c r="J43" s="5" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>対象外</t>
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(G5:G37,"対象外")</f>
+        <f>COUNTIF(G5:G39,"確認待ち")</f>
         <v/>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
@@ -4890,89 +4947,127 @@
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B45" s="4">
+        <f>COUNTIF(G5:G39,"未着手")</f>
+        <v/>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B46" s="4">
+        <f>COUNTIF(G5:G39,"対象外")</f>
+        <v/>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>資料の提供を要するか</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>資料の提供を要する</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27、No.29、No.30、No.31、No.32、No.33</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>No.1、No.3、No.5、No.7、No.8、No.9、No.11、No.15、No.16、No.17、No.21、No.24、No.26、No.27、No.29、No.30、No.31、No.35</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>提供済の資料・方針の決定で足りる</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>No.2、No.4、No.6、No.10、No.12、No.13、No.14、No.18、No.19、No.20、No.22、No.23、No.25、No.28</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="8" t="n"/>
-    </row>
-    <row r="50" ht="96" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>注1）本シートの33件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち19件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27・31）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
+      <c r="B50" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>No.2、No.4、No.6、No.10、No.12、No.13、No.14、No.18、No.19、No.20、No.22、No.23、No.25、No.32、No.33、No.34、No.28</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="8" t="n"/>
+    </row>
+    <row r="52" ht="96" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>注1）本シートの35件は、いずれも「どのデータを用いてどう算定するか」の決定を求めるものである。決定すれば本文及び図表の数値が確定する。注2）このうち18件は資料の提供を要する（業務工程管理表06シートの依頼No.）。資料の提供と本シートの決定は別の作業であり、資料が届いた時点で受託者が算定し、算定方法を本シートで確認いただく流れとなる。注3）将来推計（No.5・21・22・23・27・31）は相互に依存する。人口の基礎（No.5）→認定率の設定（No.21）→見込量（No.23・25）→保険料（No.27）の順に決定する必要があるため、No.5を最も早く決めていただきたい。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C48:J48"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="C47:J47"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="C49:J49"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G37">
+  <conditionalFormatting sqref="G5:G39">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4990,7 +5085,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
